--- a/Result/profitability/1432.xlsx
+++ b/Result/profitability/1432.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6224999999999999</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>33.205</v>
+        <v>30.19625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6187499999999999</v>
+        <v>0.5837499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>29.65625</v>
+        <v>26.70625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7537499999999999</v>
+        <v>0.6762499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>24.9875</v>
+        <v>21.33</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>17.5975</v>
+        <v>13.91625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.57</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.45375</v>
       </c>
       <c r="N6" t="n">
-        <v>11.5</v>
+        <v>7.87875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0.46</v>
+        <v>-0.41</v>
       </c>
       <c r="N7" t="n">
-        <v>7.733750000000001</v>
+        <v>5.1675</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0.28</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.30375</v>
+        <v>-0.3075</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9804,6 +9804,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>203</v>
+      </c>
+      <c r="D75" t="n">
+        <v>174</v>
+      </c>
+      <c r="E75" t="n">
+        <v>29</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-74</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-36.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-78</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-62</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02999999999999992</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.05555555555555536</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.478260869565217</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-29.45</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6731428571428572</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
